--- a/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_1/CF_M01_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,51 +471,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module. The system must be able to grow in capacity when the data volume increases. The system scales automatically as data increases.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>R_24, R_25, C_03, C_04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_12, AU_16, AU_18, AU_19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>38, 45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12a. Speed and latency; Performance</t>
+          <t>The system must be able to grow in capacity when the data volume increases.; The system scales automatically as data increases.; 12f. Capacity; 12g. Scalability</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>Cloud Storage Service; Amazon S3; Amazon Athena; AWS Glue</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6716</v>
+        <v>0.7383999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AWS is used for infrastructure. It is the set of cloud computing services that allows the creation of scalable and highly available applications.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_02, C_04</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12d. Availability and reliability; 12g. Scalability</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6922</v>
       </c>
     </row>
   </sheetData>
